--- a/public/template_data_nakes.xlsx
+++ b/public/template_data_nakes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\lapor-mas-mantri\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA415F-288B-4626-867E-DDC0FA0AD079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CAE5F3-92C6-4652-BEA1-CA4ECA285389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD5913CA-9426-40E6-A57B-02F1265C700D}"/>
+    <workbookView xWindow="1980" yWindow="2460" windowWidth="17220" windowHeight="8170" xr2:uid="{AD5913CA-9426-40E6-A57B-02F1265C700D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Sananwetan</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>08123456789</t>
+  </si>
+  <si>
+    <t>1234567891234560</t>
+  </si>
+  <si>
+    <t>1111111111111110</t>
   </si>
 </sst>
 </file>
@@ -122,12 +128,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,8 +493,8 @@
       <c r="C2">
         <v>123456</v>
       </c>
-      <c r="D2">
-        <v>1234567891234560</v>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>14</v>
@@ -509,8 +516,8 @@
       <c r="C3">
         <v>123456</v>
       </c>
-      <c r="D3">
-        <v>1111111111111110</v>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>14</v>
